--- a/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Unadjusted_Boot.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Unadjusted_Boot.xlsx
@@ -385,10 +385,10 @@
         <v>629.808</v>
       </c>
       <c r="C2">
-        <v>623.097</v>
+        <v>622.827</v>
       </c>
       <c r="D2">
-        <v>636.9930000000001</v>
+        <v>636.857</v>
       </c>
     </row>
     <row r="3">
@@ -399,10 +399,10 @@
         <v>442.324</v>
       </c>
       <c r="C3">
-        <v>435.953</v>
+        <v>435.852</v>
       </c>
       <c r="D3">
-        <v>448.591</v>
+        <v>448.668</v>
       </c>
     </row>
   </sheetData>
@@ -445,10 +445,10 @@
         <v>639.737</v>
       </c>
       <c r="C2">
-        <v>633.015</v>
+        <v>632.75</v>
       </c>
       <c r="D2">
-        <v>646.918</v>
+        <v>646.47</v>
       </c>
     </row>
     <row r="3">
@@ -459,10 +459,10 @@
         <v>449.298</v>
       </c>
       <c r="C3">
-        <v>442.88</v>
+        <v>443.187</v>
       </c>
       <c r="D3">
-        <v>455.047</v>
+        <v>455.559</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Unadjusted_Boot.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Unadjusted_Boot.xlsx
@@ -382,13 +382,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>629.808</v>
+        <v>493.758</v>
       </c>
       <c r="C2">
-        <v>622.827</v>
+        <v>486.255</v>
       </c>
       <c r="D2">
-        <v>636.857</v>
+        <v>501.628</v>
       </c>
     </row>
     <row r="3">
@@ -396,13 +396,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>442.324</v>
+        <v>267.947</v>
       </c>
       <c r="C3">
-        <v>435.852</v>
+        <v>261.301</v>
       </c>
       <c r="D3">
-        <v>448.668</v>
+        <v>274.316</v>
       </c>
     </row>
   </sheetData>
@@ -442,13 +442,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>639.737</v>
+        <v>517.204</v>
       </c>
       <c r="C2">
-        <v>632.75</v>
+        <v>509.769</v>
       </c>
       <c r="D2">
-        <v>646.47</v>
+        <v>524.8099999999999</v>
       </c>
     </row>
     <row r="3">
@@ -456,13 +456,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>449.298</v>
+        <v>280.671</v>
       </c>
       <c r="C3">
-        <v>443.187</v>
+        <v>274.024</v>
       </c>
       <c r="D3">
-        <v>455.559</v>
+        <v>287.437</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Unadjusted_Boot.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_costs_Raw-Unadjusted_Boot.xlsx
@@ -382,13 +382,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>493.758</v>
+        <v>545.188</v>
       </c>
       <c r="C2">
-        <v>486.255</v>
+        <v>538.802</v>
       </c>
       <c r="D2">
-        <v>501.628</v>
+        <v>551.818</v>
       </c>
     </row>
     <row r="3">
@@ -396,13 +396,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>267.947</v>
+        <v>287.711</v>
       </c>
       <c r="C3">
-        <v>261.301</v>
+        <v>282.029</v>
       </c>
       <c r="D3">
-        <v>274.316</v>
+        <v>293.622</v>
       </c>
     </row>
   </sheetData>
@@ -442,13 +442,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>517.204</v>
+        <v>562.1950000000001</v>
       </c>
       <c r="C2">
-        <v>509.769</v>
+        <v>555.174</v>
       </c>
       <c r="D2">
-        <v>524.8099999999999</v>
+        <v>568.841</v>
       </c>
     </row>
     <row r="3">
@@ -456,13 +456,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>280.671</v>
+        <v>296.686</v>
       </c>
       <c r="C3">
-        <v>274.024</v>
+        <v>290.885</v>
       </c>
       <c r="D3">
-        <v>287.437</v>
+        <v>302.479</v>
       </c>
     </row>
   </sheetData>
